--- a/app/data/PAKAGE1.xlsx
+++ b/app/data/PAKAGE1.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="13284" windowHeight="8675"/>
+    <workbookView windowWidth="11520" windowHeight="8675"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="195">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="215">
   <si>
     <t>الباقات المتخصصة</t>
   </si>
@@ -746,6 +746,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF95389E"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
       <t>١٩٩</t>
     </r>
     <r>
@@ -894,6 +900,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF95389E"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
       <t>١٩٩</t>
     </r>
     <r>
@@ -1012,6 +1024,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="18"/>
+        <color rgb="FF95389E"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
       <t>٢٩٩</t>
     </r>
     <r>
@@ -1951,6 +1969,334 @@
 علاج السبب الأساسي في حالات سوء الامتصاص.</t>
   </si>
   <si>
+    <t xml:space="preserve">تحليل البصمة الغذائية
+فحص عدم التحمل الغذائي
+</t>
+  </si>
+  <si>
+    <t>تحليل البصمة الغذائية هو اختبار يساعد في تحديد الأطعمة التي قد تسبب حساسية أو تفاعلات غير مرغوب فيها في الجسم. يتم عن طريق فحص الدم لمعرفة استجابة جهاز المناعة لبعض الأطعمة، مما يساعد في تحسين النظام الغذائي وتجنب الأطعمة التي قد تؤثر سلبًا على الصحة  &gt;&gt; المزيد من التفاصيل
+ما هو تحليل البصمة الغذائية؟
+ هو فحص متقدم يهدف إلى تحديد الأطعمة التي قد تُسبب للجسم استجابة مناعية غير طبيعية أو نوعًا من عدم التحمل الغذائي (Food Intolerance).
+يُظهر هذا التحليل كيف يتفاعل جهازك المناعي مع أنواع معينة من الأطعمة عن طريق قياس الأجسام المضادة من نوع IgG في الدم.
+يختلف هذا النوع من التحاليل عن اختبارات الحساسية الغذائية الحادة (IgE)، حيث يكشف عن التفاعلات المتأخرة، التي قد لا تظهر مباشرة بعد تناول الطعام، ولكنها تؤثر على الجسم خلال ساعات أو أيام.
+لماذا يُنصح بإجراء تحليل البصمة الغذائية؟
+قد تكون مصابًا بعدم تحمل غذائي دون أن تدري، حيث تظهر الأعراض بشكل مزمن وغير مباشر.
+يُوصى بإجراء تحليل البصمة الغذائية في الحالات التالية:
+الانتفاخ، الغازات، أو مشاكل في الهضم
+الصداع المتكرر أو الصداع النصفي
+التعب المزمن أو الإرهاق دون سبب واضح
+مشاكل في البشرة (حبوب، أكزيما، طفح جلدي)
+زيادة في الوزن أو صعوبة في إنقاصه
+آلام في المفاصل أو العضلات
+اضطرابات النوم أو المزاج
+ماذا يكشف تحليل البصمة الغذائية؟
+يقيس التحليل استجابة جسمك تجاه مئات من الأطعمة مثل:
+منتجات الألبان
+القمح والجلوتين
+المكسرات والبقوليات
+البيض
+اللحوم والمأكولات البحرية
+الفواكه والخضروات
+التوابل والمشروبات
+النتيجة تظهر الأطعمة التي يجب تجنبها مؤقتًا أو تقليلها، مما يساعدك على بناء نظام غذائي مخصص لصحتك.
+خطوات إجراء التحليل في مختبرات وريد الطبية
+حجز الموعد عبر الموقع أو التطبيق والهاتف
+سحب عينة دم بسيطة
+إرسال العينة إلى وحدة التحاليل المناعية
+استلام تقرير مفصّل يشمل:
+الأطعمة التي تسبب استجابة مناعية
+مستوى التفاعل لكل طعام
+توصيات غذائية مخصصة
+إمكانية الاستشارة الطبية أو التغذوية بعد النتيجة
+فوائد تحليل البصمة الغذائية
+ كشف الأطعمة المسببة للتعب أو الالتهاب المزمن
+  تحسين الهضم وصحة الأمعاء
+  المساعدة في تخفيف الوزن بشكل طبيعي
+  تقليل مشاكل الجلد والصداع والمزاج
+  بناء نظام غذائي مخصص لجسمك وحالتك الصحية</t>
+  </si>
+  <si>
+    <t xml:space="preserve">827 ريال
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> /تحليل معدل البروتينات الجزئي في الدم
+ تحليل معدل البروتينيات الحزئي</t>
+  </si>
+  <si>
+    <t xml:space="preserve">تحليل معدل البروتينات الجزئي هو فحص دم يقيس أنواع البروتينات المختلفة في الدم، مثل الألبومين والغلوبولين، ويُستخدم لتشخيص ومتابعة العديد من الحالات الصحية مثل الالتهابات، أمراض الكبد والكلى، واضطرابات الجهاز المناعي.  أهمية تحليل معدل البروتينات الجزئي
+تشخيص أمراض الكبد: يساعد على الكشف عن مشاكل في إنتاج البروتينات الأساسية.
+مراقبة صحة الكلى: فقدان بعض البروتينات عبر البول قد يشير إلى مشاكل كلوية.
+الكشف عن أمراض المناعة: بعض الأمراض مثل المايلوما المتعددة أو الاضطرابات المناعية المزمنة تؤثر على نسب الغلوبولين.
+متابعة الالتهابات المزمنة: الالتهابات تؤثر على تركيز بعض البروتينات في الدم، ما يظهر في هذا التحليل.
+القيم الطبيعية للبروتينات الجزئية
+الألبومين: 3.5 – 5.0 غرام/ديسيلتر
+الغلوبولين الكلي: 2.0 – 3.5 غرام/ديسيلتر
+النسبة بين الألبومين والغلوبولين (A/G Ratio): عادة بين 1.0 – 2.5
+ملاحظة: تختلف القيم حسب المختبر، لذلك يجب مراجعة الطبيب لتفسير النتائج بدقة.
+ارتفاع أو انخفاض البروتينات الجزئية قد يدل على:
+ارتفاع البروتين الكلي أو الغلوبولين:
+أمراض مزمنة أو التهابات طويلة الأمد
+بعض أورام البلازما أو الميلوما
+انخفاض البروتين الكلي أو الألبومين:
+أمراض الكبد أو الكلى
+سوء التغذية أو سوء الامتصاص
+حالات فقد البروتين عبر الدم أو البول
+نصائح قبل التحليل
+غالبًا لا يحتاج التحليل إلى الصيام.
+أخبر الطبيب بأي أدوية أو مكملات غذائية تتناولها، لأنها قد تؤثر على النتائج.
+اختر مختبرًا موثوقًا لضمان دقة الفحص.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">تحليل فيتامين ب 2
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">تحليل فيتامين ب2 يقيس مستوى الفيتامين B2 أو الريبوفلافين في الدم، وهو ضروري لتحويل الغذاء إلى طاقة، دعم صحة الجلد والعينين، وتقوية الجهاز العصبي  تفاصيل تحليل فيتامين ب2
+تحليل فيتامين ب2 يُجرى عن طريق سحب عينة دم من الوريد لفحص مستوى الفيتامين بدقة. عادة لا يحتاج المريض إلى صيام، لكن يجب إبلاغ الطبيب عن أي أدوية أو مكملات غذائية لأنها قد تؤثر على نتائج التحليل.
+أهمية التحليل
+يساعد التحليل في:
+تشخيص نقص أو زيادة فيتامين B2 الذي قد يؤدي إلى التعب، التهابات الفم، تقرحات الجلد، مشاكل الرؤية، واضطرابات الجهاز العصبي.
+متابعة الأشخاص الذين يتناولون مكملات غذائية أو أدوية قد تؤثر على امتصاص الفيتامين.
+تقييم سوء التغذية أو اضطرابات الامتصاص مثل مرض السيلياك.
+متى يطلب الطبيب التحليل؟
+قد يوصي الطبيب بالفحص عند:
+ظهور أعراض التعب المزمن أو ضعف التركيز.
+مشاكل في الجلد مثل التهابات أو تشققات في الشفاه والزوايا الفموية.
+اضطرابات في الرؤية أو حساسية للضوء.
+متلازمة نقص الفيتامينات أو سوء التغذية المزمن.
+متابعة الأشخاص الذين يتناولون مكملات غذائية لفترات طويلة.
+تفسير النتائج
+النقص: قد يشير إلى سوء التغذية، اضطرابات الامتصاص، مشاكل الكبد، أو تأثير بعض الأدوية.
+الزيادة: نادر الحدوث لكن قد ينتج عن تناول مكملات بجرعات عالية لفترة طويلة.
+العلاج والمتابعة
+يشمل العلاج تعديل النظام الغذائي لتضمين أطعمة غنية بفيتامين B2 مثل اللحوم، الحليب ومنتجاته، البيض، الخضروات الورقية، والحبوب الكاملة. في بعض الحالات، يصف الطبيب مكملات غذائية لضمان وصول الجرعة المناسبة. 
+    </t>
+  </si>
+  <si>
+    <r>
+      <t>١٤٩</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF95389E"/>
+        <rFont val="SimSun"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF95389E"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>ريال</t>
+    </r>
+  </si>
+  <si>
+    <t>تحليل فيتامين ب 6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">تحليل فيتامين ب6 يقيس مستوى هذا الفيتامين في الدم وهو ضروري لصحة الأعصاب وإنتاج الطاقة ودعم المنا  تفاصيل تحليل فيتامين ب6
+تحليل فيتامين ب6 يُجرى عن طريق سحب عينة دم من الوريد لفحص مستوى الفيتامين بدقة. عادة لا يحتاج المريض إلى صيام، لكن يجب إبلاغ الطبيب بأي أدوية أو مكملات غذائية لأنها قد تؤثر على دقة النتائج.
+أهمية التحليل
+يساعد التحليل على تشخيص نقص أو زيادة فيتامين ب6 الذي يؤثر على وظائف الجسم المختلفة. النقص قد يؤدي إلى التعب المزمن، ضعف التركيز، اضطرابات المزاج، التنميل أو مشاكل عصبية، في حين أن الزيادة الناتجة عن مكملات بجرعات عالية قد تسبب مشاكل عصبية وحسية.
+متى يطلب الطبيب التحليل؟
+يُوصى بإجراء التحليل عند ظهور أعراض التعب المستمر، ضعف التركيز، الاكتئاب، التنميل في اليدين أو القدمين، طفح جلدي، تشنجات عضلية، أو عند الإصابة بأمراض سوء الامتصاص مثل السيلياك أو أمراض الكبد. كما يُطلب للمتابعة الدورية للأشخاص الذين يتناولون مكملات غذائية لفترات طويلة.
+تفسير النتائج
+النقص: قد يشير إلى سوء تغذية، اضطرابات في الامتصاص، أمراض الكبد، أو تأثير بعض الأدوية.
+الزيادة: غالبًا نتيجة تناول مكملات بجرعات عالية وقد تسبب أعراضًا عصبية مثل التنميل أو فقدان الإحساس.
+العلاج والمتابعة
+يشمل العلاج تعديل النظام الغذائي لزيادة الأطعمة الغنية بفيتامين ب6 مثل الدواجن، الأسماك، البطاطس، الموز والحبوب الكاملة. في الحالات الشديدة، يصف الطبيب مكملات بجرعات محددة لضمان الحصول على المستوى المناسب للفيتامين وتجنب المضاعفات.
+ عة
+  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">تحليل الحديد
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">تحليل الحديد: يقيس مستوى الحديد في الدم، ويساعد في تشخيص الأنيميا وتقييم صحة الدم والوظائف الحيوي   ة 
+تفاصيل تحليل الحديد
+هل تشعر بتعب دائم؟ أو صداع متكرر؟ يمكن يكون السبب نقص الحديد.
+هو من التحاليل الأساسية للكشف عن فقر الدم (الأنيميا) الناتج عن نقص الحديد، وهو ضروري لتقييم صحتك العامة، خصوصًا للنساء، والأطفال، والحوامل، وكبار السن.
+ ما هو تحليل الحديد؟
+ هو فحص مخبري يُستخدم لقياس:
+مستوى الحديد في الدم
+مخزون الحديد (Ferritin)
+وأحيانًا: تشبع الترانسفرين (Transferrin Saturation)
+يُطلب التحليل عادةً ضمن مجموعة اختبارات فقر الدم (Anaemia Panel).
+ متى تحتاج تعمل تحليل الحديد؟
+ينصح الطبيب بعمل التحليل في الحالات التالية:
+التعب العام أو الإرهاق المستمر
+تساقط الشعر وضعف الأظافر
+شحوب البشرة
+الدوخة أو ضيق التنفس
+النساء أثناء الحمل أو الدورة الشهرية الشديدة
+سوء التغذية أو أمراض الجهاز الهضمي
+ أنواع تحليل الحديد المتوفرة في مختبرات وريد:
+نوع التحليل
+وصف مختصر
+Iron Serum
+يقيس كمية الحديد في الدم مباشرةً.
+Ferritin
+يقيس مخزون الحديد في الجسم.
+TIBC
+يوضح قدرة الدم على حمل الحديد.
+Transferrin Saturation
+يوضح النسبة المئوية للحديد المرتبط بالترانسفرين.
+هل ممكن أعمل تحليل الحديد من المنزل؟
+نعم، في مختبرات وريد، نوفر سحب عينات من المنزل في أكثر من 50 فرع داخل المملكة.
+فريق متخصص يزورك في منزلك لأخذ العينة، والنتائج تصلك إلكترونيًا خلال ساعات.
+ كيف أستعد لتحليل الحديد؟
+يفضل الصيام لمدة 8 ساعات (لكن ليس ضروريًا دائمًا).
+أخبر الفريق الطبي إذا كنت تستخدم مكملات حديد أو أدوية تؤثر على التحليل.
+</t>
+  </si>
+  <si>
+    <t>تحليل السمنة الجينية</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> تحليل السمنة الجينية هو تحليل علمي متطور يهدف إلى الكشف عن تأثير الجينات الوراثية على احتمالية زيادة الوزن والإصابة بالسمنة. يعتمد هذا التحليل على دراسة مجموعة من الجينات المرتبطة بتنظيم الشهية، معدل حرق الدهون، وطريقة معالجة الغذاء تحليل السمنة الجينية هو خطوة نحو رعاية صحية مخصصة تتيح لك فهم “خريطة ” جسمك الوراثية وكيفية استخدامها لصالح صحتك     المزيد من التفاصيل
+ما هو تحليل السمنة الجينية؟
+ هو فحص متقدم يتم من خلاله دراسة الجينات المرتبطة بزيادة الوزن والسمنة. يعتمد هذا التحليل على فحص الحمض النووي (DNA) للكشف عن التغيرات الجينية التي قد تؤثر على:
+معدل حرق السعرات الحرارية (الأيض)
+الشهية وتنظيم الجوع
+استجابة الجسم للتمارين الرياضية
+امتصاص الدهون والكربوهيدرات
+تأثير الهرمونات على الوزن مثل الإنسولين واللبتين
+ لماذا يعتبر تحليل السمنة الجينية مهمًا؟
+في كثير من الحالات، قد لا تكون السمنة نتيجة فقط للعادات الغذائية السيئة أو قلة النشاط البدني، بل تلعب العوامل الوراثية دورًا مهما . هذا التحليل يساعدك على :
+فهم سبب صعوبة خسارة  الوزن رغم المحاولات.
+تحديد النظام الغذائي الأنسب لجيناتك .
+تصميم برنامج رياضي وتغذوي مخصص لك بناءً على نتائجك الجينية.
+الوقاية من الأمراض المرتبطة بالسمنة مثل السكري وأمراض القلب.
+ كيف يتم إجراء التحليل ؟
+أخذ عينة DNA
+عادةً عن طريق مسحة من الخد أو عينة لعاب.
+إرسال العينة إلى المختبر
+يتم تحليلها ب استخدام تقنيات متقدمة للكشف عن الطفرات الجينية المرتبطة ب السمنة.
+الحصول على تقرير مفصل
+يشمل النتائج مع توصيات غذائية و رياضية مخصصة   .
+ لمن يُنصح بهذا التحليل ؟
+تحليل السمنة الجينية مفيد لكل من :
+يعاني من زيادة الوزن المزمنة رغم المحاولات المختلفة .
+لديه تاريخ عائلي من السمنة أو الأمراض المرتبطة بها.
+يرغب في فهم طبيعة جسمه بشكل علمي وشخصي.
+يسعى للحصول على برنامج إنقاص وزن فعّال قائم على الجينات.
+ ماذا تحتوي نتائج التحليل؟
+مؤشرات حول قابلية الجسم لزيادة الوزن.
+حساسية الجسم للكربوهيدرات والدهون.
+قدرة الجسم على الاستفادة من التمارين الهوائية والقوة.
+استعدادك الجيني لأمراض مثل السكري، مقاومة الإنسولين، أو الدهون الثلاثية العالية.
+ خدمات مختبرات وريد الطبية 
+في مختبرات وريد، نوفر تحليل السمنة الجينية باستخدام أحدث التقنيات المعتمدة عالميًا، مع :
+تقارير مفصلة وسهلة الفهم .
+استشارات طبية بعد ظهور النتائج.
+ هل تحليل السمنة الجينية دقيق وآمن؟
+نعم. التحليل يعتمد على قواعد علمية مثبتة، وتقنيات معتمدة في علم الجينوم، وهو آمن 100%  ، ولا يتطلب سحب دم أو تدخل طبي مباشر.
+ </t>
+  </si>
+  <si>
+    <r>
+      <t>١٤٩٩</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="18"/>
+        <color rgb="FF95389E"/>
+        <rFont val="SimSun"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="18"/>
+        <color rgb="FF95389E"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>ريال</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="18"/>
+        <color rgb="FF95389E"/>
+        <rFont val="SimSun"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+  </si>
+  <si>
+    <t>تحليل السكر التراكمي</t>
+  </si>
+  <si>
+    <t xml:space="preserve">تحليل السكر التراكمي : هو اختبار يستخدم بشكل رئيسي لمراقبة وإدارة مرض السكري. يعطي هذا الاختبار فكرة عن مستوى الجلوكوز (السكر) في الدم على مدى فترة طويلة، وتحديداً خلال الثلاثة أشهر الماضية، وذلك من خلال قياس نسبة السكر التي ترتبط بالهيموغلوبين داخل كريات الدم الحمراء.​
+المزيد من التفاصيل
+ما هو تحليل السكر التراكمي؟
+تحليل السكر التراكمي، المعروف أيضاً بـ HbA1c، هو اختبار دم يقيس متوسط نسبة السكر في الدم خلال فترة تتراوح بين 2 إلى 3 أشهر الماضية. يختلف هذا التحليل عن فحص السكر العادي الذي يقيس مستوى السكر في وقت معين فقط.
+لماذا يُجرى تحليل السكر التراكمي؟
+هذا التحليل مهم جداً لمرضى السكري، لأنه يساعد الأطباء والمرضى على تقييم مدى تحكمهم في مستويات السكر خلال فترة طويلة. كما يستخدم أحياناً للكشف المبكر عن مرض السكري أو مرحلة ما قبل السكري.
+كيف يُجرى تحليل السكر التراكمي؟
+يتم أخذ عينة دم بسيطة من الوريد أو الإصبع، ثم تُرسل إلى المختبر لتحليل نسبة الهيموغلوبين المرتبط بالجلوكوز (HbA1c). لا يحتاج التحليل إلى صيام مسبق.
+ما هي القيم الطبيعية لتحليل السكر التراكمي؟
+القيمة الطبيعية: أقل من 5.7%
+مرحلة ما قبل السكري: من 5.7% إلى 6.4%
+السكري: 6.5% أو أكثر
+أهمية تحليل السكر التراكمي في مراقبة مرض السكري
+متابعة فعالية العلاج سواء بالدواء أو الحمية الغذائية.
+تقليل مخاطر المضاعفات مثل مشاكل القلب، الكلى، العيون، والأعصاب.
+تعديل خطة العلاج بناءً على نتائج التحليل.
+ما هو رمز تحليل السكر التراكمي ؟
+رمز تحليل السكر التراكمي هو HbA1c، ويُستخدم لقياس متوسط مستوى السكر في الدم خلال الثلاثة أشهر الماضية، مما يساعد على متابعة مرضى السكري وتقييم فعالية العلاج والسيطرة على مستويات السكر.
+نصائح للحفاظ على معدل السكر التراكمي ضمن المستويات الصحية
+الالتزام بتعليمات الطبيب والأدوية.
+اتباع نظام غذائي صحي ومتوازن.
+ممارسة الرياضة بانتظام.
+مراقبة مستويات السكر بشكل دوري.
+    </t>
+  </si>
+  <si>
+    <t>27 ريال</t>
+  </si>
+  <si>
+    <t>تحليل الفسفور</t>
+  </si>
+  <si>
+    <t>تحليل الفسفور : يقيس مستوى الفسفور في الدم، ويعتبر الفسفور معدناً أساسياً لبناء العظام والأسنان وأيضاً يلعب دوراً في كيفية استخدام الجسم للكربوهيدرات والدهون. كما أنه ضروري لتصنيع البروتين للنمو والترميم والحفاظ على الأنسجة والخلايا.   المزيد من التفاصيل
+ما هو تحليل الفسفور؟
+ هو فحص دم يُستخدم لقياس مستوى عنصر الفسفور (Phosphorus) في الجسم، وهو من المعادن المهمة لصحة العظام والأسنان، ويلعب دورًا في إنتاج الطاقة ووظائف العضلات والأعصاب.
+لماذا يُطلب تحليل الفسفور؟
+يُطلب التحليل في الحالات التالية:
+تقييم صحة الكلى.
+متابعة حالات نقص أو زيادة الفسفور.
+تشخيص اضطرابات الغدة الجار درقية.
+مراقبة مرضى الكلى المزمن أو غسيل الكلى.
+متابعة نسبة الكالسيوم والفيتامين د المرتبطة بالفسفور.
+النسبة الطبيعية للفسفور في الدم
+للبالغين: 2.5 – 4.5 ملجم/ديسيلتر.
+للأطفال: قد تكون النسبة أعلى قليلاً.
+أسباب ارتفاع الفسفور في الدم
+أمراض الكلى المزمنة.
+نقص هرمون الغدة الجار درقية (Hypoparathyroidism).
+الإفراط في تناول المكملات أو فيتامين د.
+الحماض الكيتوني السكري.
+أسباب انخفاض الفسفور في الدم
+سوء التغذية أو سوء الامتصاص.
+فرط نشاط الغدة الجار درقية.
+الاستخدام المفرط للمدرات أو مضادات الحموضة.
+نقص فيتامين D.
+هل يحتاج تحليل الفسفور إلى صيام؟
+في بعض الحالات قد يُطلب الصيام من 6 إلى 12 ساعة، حسب تعليمات الطبيب.</t>
+  </si>
+  <si>
     <t xml:space="preserve">التحاليل الجينية
 </t>
   </si>
@@ -2047,6 +2393,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="13"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
       <t>تحليل </t>
     </r>
     <r>
@@ -2313,6 +2665,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="13"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
       <t>تحليل </t>
     </r>
     <r>
@@ -2501,7 +2859,7 @@
     <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
-  <fonts count="39">
+  <fonts count="41">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2591,6 +2949,12 @@
     <font>
       <sz val="18"/>
       <color rgb="FF717171"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color rgb="FF95389E"/>
       <name val="Arial"/>
       <charset val="134"/>
     </font>
@@ -2752,6 +3116,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="18"/>
+      <color rgb="FF95389E"/>
+      <name val="SimSun"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <b/>
       <sz val="13"/>
       <color rgb="FF000000"/>
@@ -2765,7 +3135,7 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="18"/>
+      <sz val="14"/>
       <color rgb="FF95389E"/>
       <name val="SimSun"/>
       <charset val="134"/>
@@ -3091,143 +3461,146 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="33" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="34" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="35" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="36" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="36" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="35" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="35" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="36" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="36" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="35" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="35" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="36" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="36" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="35" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="35" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="36" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="36" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="35" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="35" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="36" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="36" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="35" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="35" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="36" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="36" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="35" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -3240,12 +3613,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1" readingOrder="2"/>
     </xf>
@@ -3300,9 +3667,6 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="2"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -3321,19 +3685,31 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
     </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1" readingOrder="2"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1" readingOrder="2"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -3877,17 +4253,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C93"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="2"/>
+  <dimension ref="A1:D123"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="26.2222222222222" style="1" customWidth="1"/>
     <col min="2" max="2" width="10.4074074074074" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:3">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="1" t="s">
@@ -3901,13 +4279,13 @@
       </c>
     </row>
     <row r="3" ht="409.5" spans="1:3">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="5" t="s">
         <v>6</v>
       </c>
     </row>
@@ -3915,18 +4293,18 @@
       <c r="A4" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="5" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="5" ht="409.5" spans="1:3">
-      <c r="A5" s="5" t="s">
+      <c r="A5" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="4" t="s">
         <v>10</v>
       </c>
       <c r="C5" t="s">
@@ -3934,10 +4312,10 @@
       </c>
     </row>
     <row r="6" ht="409.5" spans="1:3">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="4" t="s">
         <v>13</v>
       </c>
       <c r="C6" t="s">
@@ -3945,13 +4323,13 @@
       </c>
     </row>
     <row r="7" ht="409.5" spans="1:3">
-      <c r="A7" s="5" t="s">
+      <c r="A7" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="C7" s="4" t="s">
         <v>16</v>
       </c>
     </row>
@@ -3959,10 +4337,10 @@
       <c r="A8" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="B8" s="7" t="s">
+      <c r="B8" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="C8" s="8" t="s">
+      <c r="C8" s="7" t="s">
         <v>19</v>
       </c>
     </row>
@@ -3970,10 +4348,10 @@
       <c r="A9" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="B9" s="7" t="s">
+      <c r="B9" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="C9" s="7" t="s">
+      <c r="C9" s="4" t="s">
         <v>22</v>
       </c>
     </row>
@@ -3981,10 +4359,10 @@
       <c r="A10" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="B10" s="7" t="s">
+      <c r="B10" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="C10" s="7" t="s">
+      <c r="C10" s="4" t="s">
         <v>25</v>
       </c>
     </row>
@@ -3992,63 +4370,63 @@
       <c r="A11" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="B11" s="9" t="s">
+      <c r="B11" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="C11" s="9" t="s">
+      <c r="C11" s="8" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="12" ht="409.5" spans="1:3">
-      <c r="A12" s="10" t="s">
+      <c r="A12" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="B12" s="7" t="s">
+      <c r="B12" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="C12" s="9" t="s">
+      <c r="C12" s="8" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="13" ht="409.5" spans="1:3">
-      <c r="A13" s="11" t="s">
+      <c r="A13" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="B13" s="7" t="s">
+      <c r="B13" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="C13" s="7" t="s">
+      <c r="C13" s="4" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="14" ht="409.5" spans="1:3">
-      <c r="A14" s="11" t="s">
+      <c r="A14" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="B14" s="7" t="s">
+      <c r="B14" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="C14" s="7" t="s">
+      <c r="C14" s="4" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="15" ht="409.5" spans="1:3">
-      <c r="A15" s="12" t="s">
+      <c r="A15" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="B15" s="7" t="s">
+      <c r="B15" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="C15" s="13"/>
+      <c r="C15" s="12"/>
     </row>
     <row r="16" ht="409.5" spans="1:3">
-      <c r="A16" s="14" t="s">
+      <c r="A16" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="B16" s="7" t="s">
+      <c r="B16" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="C16" s="15" t="s">
+      <c r="C16" s="14" t="s">
         <v>42</v>
       </c>
     </row>
@@ -4056,7 +4434,7 @@
       <c r="A17" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="B17" s="7" t="s">
+      <c r="B17" s="4" t="s">
         <v>44</v>
       </c>
       <c r="C17" t="s">
@@ -4067,21 +4445,21 @@
       <c r="A18" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="B18" s="7" t="s">
+      <c r="B18" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="C18" s="7" t="s">
+      <c r="C18" s="4" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="19" ht="78.4" spans="1:3">
+    <row r="19" ht="409.5" spans="1:3">
       <c r="A19" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="B19" s="7" t="s">
+      <c r="B19" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="C19" s="7" t="s">
+      <c r="C19" s="4" t="s">
         <v>48</v>
       </c>
     </row>
@@ -4089,10 +4467,10 @@
       <c r="A20" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="B20" s="7" t="s">
+      <c r="B20" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="C20" s="7" t="s">
+      <c r="C20" s="4" t="s">
         <v>53</v>
       </c>
     </row>
@@ -4100,32 +4478,32 @@
       <c r="A21" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B21" s="7" t="s">
+      <c r="B21" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="C21" s="7" t="s">
+      <c r="C21" s="4" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="22" ht="409.5" spans="1:3">
-      <c r="A22" s="14" t="s">
+      <c r="A22" s="13" t="s">
         <v>55</v>
       </c>
-      <c r="B22" s="7" t="s">
+      <c r="B22" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="C22" s="15" t="s">
+      <c r="C22" s="14" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="23" ht="409.5" spans="1:3">
-      <c r="A23" s="16" t="s">
+      <c r="A23" s="15" t="s">
         <v>58</v>
       </c>
-      <c r="B23" s="7" t="s">
+      <c r="B23" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="C23" s="7" t="s">
+      <c r="C23" s="4" t="s">
         <v>60</v>
       </c>
     </row>
@@ -4133,10 +4511,10 @@
       <c r="A24" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="B24" s="7" t="s">
+      <c r="B24" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="C24" s="7" t="s">
+      <c r="C24" s="4" t="s">
         <v>63</v>
       </c>
     </row>
@@ -4144,109 +4522,109 @@
       <c r="A25" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="B25" s="17" t="s">
+      <c r="B25" s="16" t="s">
         <v>64</v>
       </c>
-      <c r="C25" s="18" t="s">
+      <c r="C25" s="17" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="26" ht="409.5" spans="1:3">
-      <c r="A26" s="19" t="s">
+      <c r="A26" s="18" t="s">
         <v>66</v>
       </c>
-      <c r="B26" s="7" t="s">
+      <c r="B26" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="C26" s="7" t="s">
+      <c r="C26" s="4" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="27" ht="409.5" spans="1:3">
-      <c r="A27" s="20" t="s">
+      <c r="A27" s="19" t="s">
         <v>69</v>
       </c>
-      <c r="B27" s="7" t="s">
+      <c r="B27" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="C27" s="7" t="s">
+      <c r="C27" s="4" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="28" ht="409.5" spans="1:3">
-      <c r="A28" s="19" t="s">
+      <c r="A28" s="18" t="s">
         <v>71</v>
       </c>
-      <c r="B28" s="7" t="s">
+      <c r="B28" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="C28" s="9" t="s">
+      <c r="C28" s="8" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="29" ht="409.5" spans="1:3">
-      <c r="A29" s="20" t="s">
+      <c r="A29" s="19" t="s">
         <v>74</v>
       </c>
-      <c r="B29" s="7" t="s">
+      <c r="B29" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="C29" s="21" t="s">
+      <c r="C29" s="20" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="30" ht="409.5" spans="1:3">
-      <c r="A30" s="20" t="s">
+      <c r="A30" s="19" t="s">
         <v>77</v>
       </c>
-      <c r="B30" s="7" t="s">
+      <c r="B30" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="C30" s="7" t="s">
+      <c r="C30" s="4" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="31" ht="409.5" spans="1:3">
-      <c r="A31" s="20" t="s">
+      <c r="A31" s="19" t="s">
         <v>79</v>
       </c>
-      <c r="B31" s="7" t="s">
+      <c r="B31" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="C31" s="18" t="s">
+      <c r="C31" s="17" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="32" ht="409.5" spans="1:3">
-      <c r="A32" s="22" t="s">
+      <c r="A32" s="21" t="s">
         <v>82</v>
       </c>
-      <c r="B32" s="7" t="s">
+      <c r="B32" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="C32" s="7" t="s">
+      <c r="C32" s="4" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="33" ht="409.5" spans="1:3">
-      <c r="A33" s="23" t="s">
+      <c r="A33" s="22" t="s">
         <v>84</v>
       </c>
-      <c r="B33" s="7" t="s">
+      <c r="B33" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="C33" s="7" t="s">
+      <c r="C33" s="4" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="34" ht="409.5" spans="1:3">
-      <c r="A34" s="23" t="s">
+      <c r="A34" s="22" t="s">
         <v>87</v>
       </c>
-      <c r="B34" s="7" t="s">
+      <c r="B34" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="C34" s="7" t="s">
+      <c r="C34" s="4" t="s">
         <v>89</v>
       </c>
     </row>
@@ -4254,10 +4632,10 @@
       <c r="A35" s="6" t="s">
         <v>90</v>
       </c>
-      <c r="B35" s="7" t="s">
+      <c r="B35" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="C35" s="24" t="s">
+      <c r="C35" s="23" t="s">
         <v>92</v>
       </c>
     </row>
@@ -4265,10 +4643,10 @@
       <c r="A36" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="B36" s="7" t="s">
+      <c r="B36" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="C36" s="7" t="s">
+      <c r="C36" s="4" t="s">
         <v>95</v>
       </c>
     </row>
@@ -4276,21 +4654,21 @@
       <c r="A37" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="B37" s="7" t="s">
+      <c r="B37" s="4" t="s">
         <v>97</v>
       </c>
-      <c r="C37" s="7" t="s">
+      <c r="C37" s="4" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="38" ht="251.2" spans="1:3">
+    <row r="38" ht="409.5" spans="1:3">
       <c r="A38" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="B38" s="7" t="s">
+      <c r="B38" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="C38" s="7" t="s">
+      <c r="C38" s="4" t="s">
         <v>63</v>
       </c>
     </row>
@@ -4298,10 +4676,10 @@
       <c r="A39" s="6" t="s">
         <v>101</v>
       </c>
-      <c r="B39" s="7" t="s">
+      <c r="B39" s="4" t="s">
         <v>102</v>
       </c>
-      <c r="C39" s="7" t="s">
+      <c r="C39" s="4" t="s">
         <v>103</v>
       </c>
     </row>
@@ -4309,21 +4687,21 @@
       <c r="A40" s="6" t="s">
         <v>104</v>
       </c>
-      <c r="B40" s="7" t="s">
+      <c r="B40" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="C40" s="7" t="s">
+      <c r="C40" s="4" t="s">
         <v>106</v>
       </c>
     </row>
     <row r="41" ht="409.5" spans="1:3">
-      <c r="A41" s="20" t="s">
+      <c r="A41" s="19" t="s">
         <v>107</v>
       </c>
-      <c r="B41" s="7" t="s">
+      <c r="B41" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="C41" s="7" t="s">
+      <c r="C41" s="4" t="s">
         <v>109</v>
       </c>
     </row>
@@ -4331,71 +4709,71 @@
       <c r="A42" s="6" t="s">
         <v>110</v>
       </c>
-      <c r="B42" s="7" t="s">
+      <c r="B42" s="4" t="s">
         <v>111</v>
       </c>
-      <c r="C42" s="9" t="s">
+      <c r="C42" s="8" t="s">
         <v>112</v>
       </c>
     </row>
     <row r="43" ht="409.5" spans="1:3">
-      <c r="A43" s="25" t="s">
+      <c r="A43" s="24" t="s">
         <v>113</v>
       </c>
-      <c r="B43" s="7" t="s">
+      <c r="B43" s="4" t="s">
         <v>114</v>
       </c>
-      <c r="C43" s="9" t="s">
+      <c r="C43" s="8" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="44" ht="280" spans="1:3">
+    <row r="44" ht="409.5" spans="1:3">
       <c r="A44" s="6" t="s">
         <v>115</v>
       </c>
-      <c r="B44" s="7" t="s">
+      <c r="B44" s="4" t="s">
         <v>116</v>
       </c>
-      <c r="C44" s="9" t="s">
+      <c r="C44" s="8" t="s">
         <v>112</v>
       </c>
     </row>
     <row r="47" spans="1:3">
-      <c r="A47" s="26" t="s">
+      <c r="A47" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="B47" s="26"/>
-      <c r="C47" s="26"/>
+      <c r="B47" s="2"/>
+      <c r="C47" s="2"/>
     </row>
     <row r="48" spans="1:3">
-      <c r="A48" s="26"/>
-      <c r="B48" s="26"/>
-      <c r="C48" s="26"/>
+      <c r="A48" s="2"/>
+      <c r="B48" s="2"/>
+      <c r="C48" s="2"/>
     </row>
     <row r="49" spans="1:3">
-      <c r="A49" s="26"/>
-      <c r="B49" s="26"/>
-      <c r="C49" s="26"/>
+      <c r="A49" s="2"/>
+      <c r="B49" s="2"/>
+      <c r="C49" s="2"/>
     </row>
     <row r="50" ht="409.5" spans="1:3">
       <c r="A50" s="6" t="s">
         <v>118</v>
       </c>
-      <c r="B50" s="7" t="s">
+      <c r="B50" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="C50" s="7" t="s">
+      <c r="C50" s="4" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="51" ht="409.5" spans="1:3">
-      <c r="A51" s="27" t="s">
+      <c r="A51" s="25" t="s">
         <v>121</v>
       </c>
-      <c r="B51" s="7" t="s">
+      <c r="B51" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="C51" s="28" t="s">
+      <c r="C51" s="26" t="s">
         <v>123</v>
       </c>
     </row>
@@ -4403,21 +4781,21 @@
       <c r="A52" s="6" t="s">
         <v>124</v>
       </c>
-      <c r="B52" s="7" t="s">
+      <c r="B52" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="C52" s="7" t="s">
+      <c r="C52" s="4" t="s">
         <v>126</v>
       </c>
     </row>
     <row r="53" ht="409.5" spans="1:3">
-      <c r="A53" s="19" t="s">
+      <c r="A53" s="18" t="s">
         <v>127</v>
       </c>
-      <c r="B53" s="7" t="s">
+      <c r="B53" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="C53" s="29" t="s">
+      <c r="C53" s="27" t="s">
         <v>129</v>
       </c>
     </row>
@@ -4425,10 +4803,10 @@
       <c r="A54" s="6" t="s">
         <v>130</v>
       </c>
-      <c r="B54" s="7" t="s">
+      <c r="B54" s="4" t="s">
         <v>131</v>
       </c>
-      <c r="C54" s="7" t="s">
+      <c r="C54" s="4" t="s">
         <v>132</v>
       </c>
     </row>
@@ -4436,10 +4814,10 @@
       <c r="A57" s="6" t="s">
         <v>133</v>
       </c>
-      <c r="B57" s="7" t="s">
+      <c r="B57" s="4" t="s">
         <v>134</v>
       </c>
-      <c r="C57" s="7" t="s">
+      <c r="C57" s="4" t="s">
         <v>135</v>
       </c>
     </row>
@@ -4447,10 +4825,10 @@
       <c r="A58" s="6" t="s">
         <v>136</v>
       </c>
-      <c r="B58" s="7" t="s">
+      <c r="B58" s="4" t="s">
         <v>137</v>
       </c>
-      <c r="C58" s="7" t="s">
+      <c r="C58" s="4" t="s">
         <v>135</v>
       </c>
     </row>
@@ -4458,21 +4836,21 @@
       <c r="A59" s="6" t="s">
         <v>138</v>
       </c>
-      <c r="B59" s="7" t="s">
+      <c r="B59" s="4" t="s">
         <v>139</v>
       </c>
-      <c r="C59" s="7" t="s">
+      <c r="C59" s="4" t="s">
         <v>132</v>
       </c>
     </row>
     <row r="60" ht="409.5" spans="1:3">
-      <c r="A60" s="30" t="s">
+      <c r="A60" s="28" t="s">
         <v>140</v>
       </c>
-      <c r="B60" s="7" t="s">
+      <c r="B60" s="4" t="s">
         <v>141</v>
       </c>
-      <c r="C60" s="7" t="s">
+      <c r="C60" s="4" t="s">
         <v>135</v>
       </c>
     </row>
@@ -4480,21 +4858,21 @@
       <c r="A61" s="6" t="s">
         <v>142</v>
       </c>
-      <c r="B61" s="7" t="s">
+      <c r="B61" s="4" t="s">
         <v>143</v>
       </c>
-      <c r="C61" s="7" t="s">
+      <c r="C61" s="4" t="s">
         <v>144</v>
       </c>
     </row>
     <row r="62" ht="409.5" spans="1:3">
-      <c r="A62" s="19" t="s">
+      <c r="A62" s="18" t="s">
         <v>145</v>
       </c>
-      <c r="B62" s="7" t="s">
+      <c r="B62" s="4" t="s">
         <v>146</v>
       </c>
-      <c r="C62" s="7" t="s">
+      <c r="C62" s="4" t="s">
         <v>144</v>
       </c>
     </row>
@@ -4502,10 +4880,10 @@
       <c r="A63" s="6" t="s">
         <v>147</v>
       </c>
-      <c r="B63" s="7" t="s">
+      <c r="B63" s="4" t="s">
         <v>148</v>
       </c>
-      <c r="C63" s="7" t="s">
+      <c r="C63" s="4" t="s">
         <v>144</v>
       </c>
     </row>
@@ -4513,10 +4891,10 @@
       <c r="A64" s="6" t="s">
         <v>149</v>
       </c>
-      <c r="B64" s="7" t="s">
+      <c r="B64" s="4" t="s">
         <v>150</v>
       </c>
-      <c r="C64" s="31" t="s">
+      <c r="C64" s="29" t="s">
         <v>151</v>
       </c>
     </row>
@@ -4524,10 +4902,10 @@
       <c r="A65" s="6" t="s">
         <v>152</v>
       </c>
-      <c r="B65" s="7" t="s">
+      <c r="B65" s="4" t="s">
         <v>153</v>
       </c>
-      <c r="C65" s="7" t="s">
+      <c r="C65" s="4" t="s">
         <v>154</v>
       </c>
     </row>
@@ -4535,7 +4913,7 @@
       <c r="A66" s="6" t="s">
         <v>155</v>
       </c>
-      <c r="B66" s="7" t="s">
+      <c r="B66" s="4" t="s">
         <v>156</v>
       </c>
       <c r="C66" t="s">
@@ -4546,21 +4924,21 @@
       <c r="A67" s="6" t="s">
         <v>158</v>
       </c>
-      <c r="B67" s="7" t="s">
+      <c r="B67" s="4" t="s">
         <v>159</v>
       </c>
-      <c r="C67" s="7" t="s">
+      <c r="C67" s="4" t="s">
         <v>154</v>
       </c>
     </row>
     <row r="68" ht="409.5" spans="1:3">
-      <c r="A68" s="30" t="s">
+      <c r="A68" s="28" t="s">
         <v>160</v>
       </c>
-      <c r="B68" s="7" t="s">
+      <c r="B68" s="4" t="s">
         <v>161</v>
       </c>
-      <c r="C68" s="32" t="s">
+      <c r="C68" s="30" t="s">
         <v>162</v>
       </c>
     </row>
@@ -4568,10 +4946,10 @@
       <c r="A69" s="6" t="s">
         <v>163</v>
       </c>
-      <c r="B69" s="7" t="s">
+      <c r="B69" s="4" t="s">
         <v>164</v>
       </c>
-      <c r="C69" s="32" t="s">
+      <c r="C69" s="30" t="s">
         <v>162</v>
       </c>
     </row>
@@ -4579,169 +4957,369 @@
       <c r="A70" s="6" t="s">
         <v>165</v>
       </c>
-      <c r="B70" s="7" t="s">
+      <c r="B70" s="4" t="s">
         <v>166</v>
       </c>
-      <c r="C70" s="7" t="s">
+      <c r="C70" s="4" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="73" spans="1:3">
-      <c r="A73" s="33" t="s">
+    <row r="71" ht="409.5" spans="1:3">
+      <c r="A71" s="6" t="s">
         <v>167</v>
       </c>
-      <c r="B73" s="26"/>
-      <c r="C73" s="26"/>
-    </row>
-    <row r="74" spans="1:3">
-      <c r="A74" s="26"/>
-      <c r="B74" s="26"/>
-      <c r="C74" s="26"/>
-    </row>
-    <row r="75" spans="1:3">
-      <c r="A75" s="26"/>
-      <c r="B75" s="26"/>
-      <c r="C75" s="26"/>
-    </row>
-    <row r="76" ht="409.5" spans="1:2">
-      <c r="A76" s="6" t="s">
+      <c r="B71" s="4" t="s">
         <v>168</v>
       </c>
-      <c r="B76" s="7" t="s">
+      <c r="C71" s="4" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="77" ht="409.5" spans="1:2">
-      <c r="A77" s="34" t="s">
+    <row r="72" ht="409.5" spans="1:3">
+      <c r="A72" s="6" t="s">
         <v>170</v>
       </c>
-      <c r="B77" s="7" t="s">
+      <c r="B72" s="4" t="s">
         <v>171</v>
       </c>
-    </row>
-    <row r="78" ht="21.6" spans="1:3">
-      <c r="A78" s="35" t="s">
+      <c r="C72" s="4" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="73" ht="409.5" spans="1:3">
+      <c r="A73" s="6" t="s">
         <v>172</v>
       </c>
-      <c r="B78" s="35"/>
-      <c r="C78" s="35"/>
-    </row>
-    <row r="79" ht="409.5" spans="1:3">
-      <c r="A79" s="36" t="s">
+      <c r="B73" s="4" t="s">
         <v>173</v>
       </c>
-      <c r="B79" s="7" t="s">
+      <c r="C73" s="31" t="s">
         <v>174</v>
       </c>
-      <c r="C79" s="7"/>
-    </row>
-    <row r="80" ht="409.5" spans="1:2">
-      <c r="A80" s="34" t="s">
+    </row>
+    <row r="74" ht="409.5" spans="1:3">
+      <c r="A74" s="32" t="s">
         <v>175</v>
       </c>
-      <c r="B80" s="37" t="s">
+      <c r="B74" s="4" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="81" spans="1:3">
-      <c r="A81" s="38" t="s">
+      <c r="C74" s="4" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="75" ht="409.5" spans="1:3">
+      <c r="A75" s="6" t="s">
         <v>177</v>
       </c>
-      <c r="B81" s="38"/>
-      <c r="C81" s="38"/>
+      <c r="B75" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="C75" s="4" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="76" ht="409.5" spans="1:3">
+      <c r="A76" s="32" t="s">
+        <v>179</v>
+      </c>
+      <c r="B76" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="C76" s="33" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="77" ht="409.5" spans="1:3">
+      <c r="A77" s="32" t="s">
+        <v>182</v>
+      </c>
+      <c r="B77" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="C77" s="33" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="78" ht="409.5" spans="1:4">
+      <c r="A78" s="32" t="s">
+        <v>185</v>
+      </c>
+      <c r="B78" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="C78" s="34" t="s">
+        <v>162</v>
+      </c>
+      <c r="D78" s="34"/>
+    </row>
+    <row r="79" ht="22.8" spans="1:3">
+      <c r="A79" s="32"/>
+      <c r="B79" s="4"/>
+      <c r="C79" s="33"/>
+    </row>
+    <row r="80" ht="22.8" spans="1:3">
+      <c r="A80" s="32"/>
+      <c r="B80" s="4"/>
+      <c r="C80" s="33"/>
+    </row>
+    <row r="81" ht="22.8" spans="1:3">
+      <c r="A81" s="32"/>
+      <c r="B81" s="4"/>
+      <c r="C81" s="33"/>
     </row>
     <row r="82" ht="22.8" spans="1:3">
-      <c r="A82" s="38"/>
-      <c r="B82" s="38"/>
-      <c r="C82" s="38"/>
-    </row>
-    <row r="83" ht="409.5" spans="1:2">
-      <c r="A83" s="6" t="s">
-        <v>178</v>
-      </c>
-      <c r="B83" s="7" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="84" ht="409.5" spans="1:2">
-      <c r="A84" s="6" t="s">
-        <v>180</v>
-      </c>
-      <c r="B84" s="7" t="s">
-        <v>181</v>
-      </c>
+      <c r="A82" s="32"/>
+      <c r="B82" s="4"/>
+      <c r="C82" s="33"/>
+    </row>
+    <row r="83" ht="22.8" spans="1:3">
+      <c r="A83" s="32"/>
+      <c r="B83" s="4"/>
+      <c r="C83" s="33"/>
+    </row>
+    <row r="84" ht="22.8" spans="1:3">
+      <c r="A84" s="32"/>
+      <c r="B84" s="4"/>
+      <c r="C84" s="33"/>
+    </row>
+    <row r="85" spans="1:3">
+      <c r="A85" s="6"/>
+      <c r="B85" s="4"/>
+      <c r="C85" s="4"/>
     </row>
     <row r="86" spans="1:3">
-      <c r="A86" s="33" t="s">
-        <v>182</v>
-      </c>
-      <c r="B86" s="26"/>
-      <c r="C86" s="26"/>
+      <c r="A86" s="6"/>
+      <c r="B86" s="4"/>
+      <c r="C86" s="4"/>
     </row>
     <row r="87" spans="1:3">
-      <c r="A87" s="26"/>
-      <c r="B87" s="26"/>
-      <c r="C87" s="26"/>
+      <c r="A87" s="6"/>
+      <c r="B87" s="4"/>
+      <c r="C87" s="4"/>
     </row>
     <row r="88" spans="1:3">
-      <c r="A88" s="26"/>
-      <c r="B88" s="26"/>
-      <c r="C88" s="26"/>
-    </row>
-    <row r="89" ht="409.5" spans="1:3">
-      <c r="A89" s="6" t="s">
-        <v>183</v>
-      </c>
-      <c r="B89" s="7" t="s">
-        <v>184</v>
-      </c>
-      <c r="C89" s="29" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="90" ht="409.5" spans="1:3">
-      <c r="A90" s="6" t="s">
-        <v>186</v>
-      </c>
-      <c r="B90" s="7" t="s">
+      <c r="A88" s="6"/>
+      <c r="B88" s="4"/>
+      <c r="C88" s="4"/>
+    </row>
+    <row r="89" spans="1:3">
+      <c r="A89" s="6"/>
+      <c r="B89" s="4"/>
+      <c r="C89" s="4"/>
+    </row>
+    <row r="90" spans="1:3">
+      <c r="A90" s="6"/>
+      <c r="B90" s="4"/>
+      <c r="C90" s="4"/>
+    </row>
+    <row r="91" spans="1:3">
+      <c r="A91" s="6"/>
+      <c r="B91" s="4"/>
+      <c r="C91" s="4"/>
+    </row>
+    <row r="92" spans="1:3">
+      <c r="A92" s="6"/>
+      <c r="B92" s="4"/>
+      <c r="C92" s="4"/>
+    </row>
+    <row r="93" spans="1:3">
+      <c r="A93" s="6"/>
+      <c r="B93" s="4"/>
+      <c r="C93" s="4"/>
+    </row>
+    <row r="94" spans="1:3">
+      <c r="A94" s="6"/>
+      <c r="B94" s="4"/>
+      <c r="C94" s="4"/>
+    </row>
+    <row r="95" spans="1:3">
+      <c r="A95" s="6"/>
+      <c r="B95" s="4"/>
+      <c r="C95" s="4"/>
+    </row>
+    <row r="96" spans="1:3">
+      <c r="A96" s="6"/>
+      <c r="B96" s="4"/>
+      <c r="C96" s="4"/>
+    </row>
+    <row r="97" spans="1:3">
+      <c r="A97" s="6"/>
+      <c r="B97" s="4"/>
+      <c r="C97" s="4"/>
+    </row>
+    <row r="98" spans="1:3">
+      <c r="A98" s="6"/>
+      <c r="B98" s="4"/>
+      <c r="C98" s="4"/>
+    </row>
+    <row r="99" spans="1:3">
+      <c r="A99" s="6"/>
+      <c r="B99" s="4"/>
+      <c r="C99" s="4"/>
+    </row>
+    <row r="100" spans="1:3">
+      <c r="A100" s="6"/>
+      <c r="B100" s="4"/>
+      <c r="C100" s="4"/>
+    </row>
+    <row r="103" spans="1:3">
+      <c r="A103" s="35" t="s">
         <v>187</v>
       </c>
-      <c r="C90" s="7" t="s">
+      <c r="B103" s="2"/>
+      <c r="C103" s="2"/>
+    </row>
+    <row r="104" spans="1:3">
+      <c r="A104" s="2"/>
+      <c r="B104" s="2"/>
+      <c r="C104" s="2"/>
+    </row>
+    <row r="105" spans="1:3">
+      <c r="A105" s="2"/>
+      <c r="B105" s="2"/>
+      <c r="C105" s="2"/>
+    </row>
+    <row r="106" ht="409.5" spans="1:2">
+      <c r="A106" s="6" t="s">
         <v>188</v>
       </c>
-    </row>
-    <row r="91" ht="409.5" spans="1:3">
-      <c r="A91" s="6" t="s">
+      <c r="B106" s="4" t="s">
         <v>189</v>
       </c>
-      <c r="B91" s="37" t="s">
+    </row>
+    <row r="107" ht="409.5" spans="1:2">
+      <c r="A107" s="36" t="s">
         <v>190</v>
       </c>
-      <c r="C91" s="7"/>
-    </row>
-    <row r="92" ht="409.5" spans="1:2">
-      <c r="A92" s="34" t="s">
+      <c r="B107" s="4" t="s">
         <v>191</v>
       </c>
-      <c r="B92" s="7" t="s">
+    </row>
+    <row r="108" ht="21.6" spans="1:3">
+      <c r="A108" s="37" t="s">
         <v>192</v>
       </c>
-    </row>
-    <row r="93" ht="409.5" spans="1:2">
-      <c r="A93" s="6" t="s">
+      <c r="B108" s="37"/>
+      <c r="C108" s="37"/>
+    </row>
+    <row r="109" ht="409.5" spans="1:3">
+      <c r="A109" s="38" t="s">
         <v>193</v>
       </c>
-      <c r="B93" s="7" t="s">
+      <c r="B109" s="4" t="s">
         <v>194</v>
       </c>
+      <c r="C109" s="4"/>
+    </row>
+    <row r="110" ht="409.5" spans="1:2">
+      <c r="A110" s="36" t="s">
+        <v>195</v>
+      </c>
+      <c r="B110" s="39" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="111" spans="1:3">
+      <c r="A111" s="40" t="s">
+        <v>197</v>
+      </c>
+      <c r="B111" s="40"/>
+      <c r="C111" s="40"/>
+    </row>
+    <row r="112" spans="1:3">
+      <c r="A112" s="40"/>
+      <c r="B112" s="40"/>
+      <c r="C112" s="40"/>
+    </row>
+    <row r="113" ht="409.5" spans="1:2">
+      <c r="A113" s="6" t="s">
+        <v>198</v>
+      </c>
+      <c r="B113" s="4" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="114" ht="409.5" spans="1:2">
+      <c r="A114" s="6" t="s">
+        <v>200</v>
+      </c>
+      <c r="B114" s="4" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="116" spans="1:3">
+      <c r="A116" s="35" t="s">
+        <v>202</v>
+      </c>
+      <c r="B116" s="2"/>
+      <c r="C116" s="2"/>
+    </row>
+    <row r="117" spans="1:3">
+      <c r="A117" s="2"/>
+      <c r="B117" s="2"/>
+      <c r="C117" s="2"/>
+    </row>
+    <row r="118" spans="1:3">
+      <c r="A118" s="2"/>
+      <c r="B118" s="2"/>
+      <c r="C118" s="2"/>
+    </row>
+    <row r="119" ht="409.5" spans="1:3">
+      <c r="A119" s="6" t="s">
+        <v>203</v>
+      </c>
+      <c r="B119" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C119" s="27" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="120" ht="409.5" spans="1:3">
+      <c r="A120" s="6" t="s">
+        <v>206</v>
+      </c>
+      <c r="B120" s="4" t="s">
+        <v>207</v>
+      </c>
+      <c r="C120" s="4" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="121" ht="409.5" spans="1:3">
+      <c r="A121" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="B121" s="39" t="s">
+        <v>210</v>
+      </c>
+      <c r="C121" s="4"/>
+    </row>
+    <row r="122" ht="409.5" spans="1:2">
+      <c r="A122" s="36" t="s">
+        <v>211</v>
+      </c>
+      <c r="B122" s="4" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="123" ht="409.5" spans="1:2">
+      <c r="A123" s="6" t="s">
+        <v>213</v>
+      </c>
+      <c r="B123" s="4" t="s">
+        <v>214</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
-    <mergeCell ref="A78:C78"/>
+  <mergeCells count="6">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A108:C108"/>
     <mergeCell ref="A47:C49"/>
-    <mergeCell ref="A73:C75"/>
-    <mergeCell ref="A81:C82"/>
-    <mergeCell ref="A86:C88"/>
+    <mergeCell ref="A103:C105"/>
+    <mergeCell ref="A111:C112"/>
+    <mergeCell ref="A116:C118"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
